--- a/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
+++ b/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
@@ -699,7 +699,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.32.0</t>
+          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.33.0</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.32.0</t>
+          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.33.0</t>
         </is>
       </c>
     </row>

--- a/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
+++ b/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
@@ -699,7 +699,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.33.0</t>
+          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.34.0</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.33.0</t>
+          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.34.0</t>
         </is>
       </c>
     </row>

--- a/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
+++ b/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
@@ -699,7 +699,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.34.0</t>
+          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.35.0</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.34.0</t>
+          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.35.0</t>
         </is>
       </c>
     </row>

--- a/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
+++ b/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
@@ -699,7 +699,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.35.0</t>
+          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.36.0</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.35.0</t>
+          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.36.0</t>
         </is>
       </c>
     </row>

--- a/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
+++ b/documentos/Cronograma_de_Actividades_MediTime_2026.xlsx
@@ -699,7 +699,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.36.0</t>
+          <t>Proyecto de Grado PGC (Noveno Semestre) — Vigencia 2026 | MediTime v2.37.0</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.36.0</t>
+          <t>Visión Macro-Evolutiva Anual (Febrero – Noviembre 2026) | MediTime v2.37.0</t>
         </is>
       </c>
     </row>
